--- a/src/make_dummy_data/科目一覧.xlsx
+++ b/src/make_dummy_data/科目一覧.xlsx
@@ -453,436 +453,424 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>332586</t>
+          <t>4957-8631</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>雰囲気でわかる量子力学</t>
+          <t>CC入れすぎ問題研究</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2020- 2025</t>
+          <t>2020- 2021  2023-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>毎年少しずつスライドが増える</t>
+          <t>チョークを落としても動じない</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8938-7174</t>
+          <t>692156</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>雰囲気プレゼン実習</t>
+          <t>再起動信仰論</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2020 - 2022,2025</t>
+          <t>2022-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>質問されたらうれしい</t>
+          <t>学生より少しだけ早起きする</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8281-3841</t>
+          <t>012658</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>うっかり工学入門</t>
+          <t>依存関係地獄学</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2020 - 2024</t>
+          <t>2020 - 2021, 2023 - 2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>チョークを落としても動じない</t>
+          <t>学生の表情から進度を推測する</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1748-7022</t>
+          <t>2569-5836</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>誰かがやるだろう理論</t>
+          <t>なんでも再利用工学</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2020 -2022 2025</t>
+          <t>2020 ,2024 - 2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>学生の表情から進度を推測する</t>
+          <t>質問されなくても気にしない</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3475-0118</t>
+          <t>3425-1507</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>無料だけ使う戦略論</t>
+          <t>パスワード忘却史</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2020- 2024</t>
+          <t>2020 ; 2022 - 2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>最後の5分はだいたい足りない</t>
+          <t>学生の眠気とは長い付き合い</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>588104</t>
+          <t>539999</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>思いつき実験学</t>
+          <t>眠気制御理論</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2020-2023, 2025</t>
+          <t>2020 - 2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>板書はゆっくり、消すのはもっとゆっくり</t>
+          <t>質問がなくても気にしないふりをする</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2727-4078</t>
+          <t>941909</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>忘却曲線活用術</t>
+          <t>思いつき実験学</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2020-2025</t>
+          <t>2020   2022-2023   2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>とりあえず今日もなんとかする</t>
+          <t>沈黙が続いたら自分で答える</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3594-9108</t>
+          <t>649948</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>直感だけで解く微積分</t>
+          <t>会議短縮失敗学</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2020, 2022 -2025</t>
+          <t>2020 ; 2022 - 2023 ; 2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>質問されたらうれしい</t>
+          <t>難しい式ほど「気持ち」を説明する</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2638-0710</t>
+          <t>9338-2763</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>いい感じに終わらせる学</t>
+          <t>レポート生成錬金術</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2020 -2022  2024</t>
+          <t>2021-2023, 2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>難しい式ほど「気持ち」を説明する</t>
+          <t>静かな教室にも慣れる</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0152-9353</t>
+          <t>2423-6699</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>深夜テンション工学</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2021 -2025</t>
-        </is>
-      </c>
+          <t>よろしくお願いします学</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>パソコンは授業前に再起動</t>
+          <t>わからないと言われてもめげない</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>016268</t>
+          <t>3437-0410</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>説明書未読文化</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2020 - 2025</t>
-        </is>
-      </c>
+          <t>締切延長交渉術</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>学生の眠気とは長い付き合い</t>
+          <t>沈黙が続いたら自分で答える</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5533-8419</t>
+          <t>266781</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>三日坊主持続可能性</t>
+          <t>仮フォルダ恒久保存論</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2020 -2024</t>
+          <t>2021-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>マイクのスイッチは先に確認</t>
+          <t>わからない顔を見逃さない（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>807518</t>
+          <t>195588</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>締切延長交渉術</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>目的を見失う設計論</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2020- 2022,2024- 2025</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>話がそれても授業の一部</t>
+          <t>例え話でだいたい乗り切る</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9771-5348</t>
+          <t>625531</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>エラー文鑑賞学</t>
+          <t>最終版（仮）研究</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2022- 2024</t>
+          <t>2020 - 2021 2023 2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>マイクのスイッチは先に確認</t>
+          <t>毎年少しずつスライドが増える</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7026-2663</t>
+          <t>6603-8449</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>目的を見失う設計論</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2020- 2025</t>
-        </is>
-      </c>
+          <t>うっかり工学入門</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>教室の時計を信じすぎない</t>
+          <t>わからない顔を見逃さない（たぶん）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>532525</t>
+          <t>052204</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>締切直前行動科学</t>
+          <t>気づかなかったふり実践</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2020 -2025</t>
+          <t>2020 -2022 ; 2024- 2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>質問されなくても気にしない</t>
+          <t>脱線しても最後は戻る</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>809217</t>
+          <t>041446</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>突然のやる気論</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2021- 2025</t>
-        </is>
-      </c>
+          <t>互換性崩壊史</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>難しい式ほど「気持ち」を説明する</t>
+          <t>時間通りに終わる努力はする</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0920-1082</t>
+          <t>0153-0205</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>バグとの対話実践</t>
+          <t>買って満足経済学</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2022 - 2025</t>
+          <t>2021 ; 2023 ; 2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>難しい話ほど雑談から入る</t>
+          <t>わからないと言われてもめげない</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3227-7967</t>
+          <t>1795-7979</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>なんとかなる確率論</t>
+          <t>雑なまとめ方特講</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2021- 2022, 2024- 2025</t>
+          <t>2020 ; 2022 -2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>学生の眠気とは長い付き合い</t>
+          <t>最後の5分はだいたい足りない</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9877-8323</t>
+          <t>3185-1508</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>質疑応答回避技法</t>
+          <t>エラー文鑑賞学</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2020- 2021, 2023 -2025</t>
+          <t>2020- 2021;2023 -2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>脱線しても最後は戻る</t>
+          <t>板書はゆっくり、消すのはもっとゆっくり</t>
         </is>
       </c>
     </row>
